--- a/Data/Results/Visualizations/Visualization_Category_Index.xlsx
+++ b/Data/Results/Visualizations/Visualization_Category_Index.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,12 +430,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Paired Workbooks</t>
         </is>
@@ -436,7 +448,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -450,296 +462,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF19"/>
+  <dimension ref="A1:BF39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>pair_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>pair_number</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pair_class</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>operation_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>workbook_path</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ev_tat_min</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ice_tat_min</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ev_distance_km</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ice_distance_km</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ev_moving_speed_kmh</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ice_moving_speed_kmh</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tat_min_diff</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>distance_km_diff</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>moving_speed_kmh_diff</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>stationary_time_min_diff</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ev_charging_refueling_time_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ice_charging_refueling_time_min</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>charging_refueling_time_diff_min</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ev_charging_refueling_distance_km</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ice_charging_refueling_distance_km</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>charging_refueling_distance_diff_km</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ev_stop_time_min</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ice_stop_time_min</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>stop_time_diff_min</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ev_stop_distance_km</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ice_stop_distance_km</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stop_distance_diff_km</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ev_idle_time_min</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ice_idle_time_min</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>idle_time_diff_min</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ev_idle_distance_km</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ice_idle_distance_km</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>idle_distance_diff_km</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ev_inch_time_min</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ice_inch_time_min</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>inch_time_diff_min</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ev_inch_distance_km</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>ice_inch_distance_km</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>inch_distance_diff_km</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>ev_acc_time_min</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ice_acc_time_min</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>acc_time_diff_min</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>ev_acc_distance_km</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ice_acc_distance_km</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>acc_distance_diff_km</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>ev_dec_time_min</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>ice_dec_time_min</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dec_time_diff_min</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>ev_dec_distance_km</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>ice_dec_distance_km</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dec_distance_diff_km</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>ev_cruise_time_min</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>ice_cruise_time_min</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>cruise_time_diff_min</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>ev_cruise_distance_km</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>ice_cruise_distance_km</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>cruise_distance_diff_km</t>
         </is>
@@ -756,7 +768,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -766,169 +778,169 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chennai to Pondicherry</t>
+          <t>SilkBoard to Madhuravoyal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026\PAIR_001_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-07-2026_to_29-07-2026\PAIR_001_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>240.4436333333333</v>
+        <v>98.16888333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>274.35</v>
+        <v>85.5448</v>
       </c>
       <c r="I2" t="n">
-        <v>148.1987690237775</v>
+        <v>102.5403079815431</v>
       </c>
       <c r="J2" t="n">
-        <v>148.1254196841063</v>
+        <v>102.5404226319246</v>
       </c>
       <c r="K2" t="n">
-        <v>41.58535677727425</v>
+        <v>76.08025778994646</v>
       </c>
       <c r="L2" t="n">
-        <v>43.13601932523515</v>
+        <v>76.61984720324178</v>
       </c>
       <c r="M2" t="n">
-        <v>-33.90636666666671</v>
+        <v>12.62408333333333</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07334933967118218</v>
+        <v>-0.0001146503815050437</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.550662547960897</v>
+        <v>-0.5395894132953174</v>
       </c>
       <c r="P2" t="n">
-        <v>13.56666666666666</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>25.88333333333333</v>
+        <v>10.5</v>
       </c>
       <c r="X2" t="n">
-        <v>13.56666666666667</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.31666666666666</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3556868609874803</v>
+        <v>0.02708574234946004</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.1105839661259325</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.2073716941169366</v>
+        <v>-0.08349822377647247</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>6.85</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.25</v>
+        <v>6.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.03453093426685515</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>0.03453093426685515</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.016666666666667</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.716666666666667</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.300000000000001</v>
+        <v>0.5500000000000004</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.6265751975894123</v>
+        <v>0.08000017609170872</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5759078527107181</v>
+        <v>0.1014311759756502</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.05066734487869418</v>
+        <v>-0.02143099988394148</v>
       </c>
       <c r="AO2" t="n">
-        <v>56.05</v>
+        <v>15.36666666666667</v>
       </c>
       <c r="AP2" t="n">
-        <v>25.13333333333333</v>
+        <v>10.36666666666667</v>
       </c>
       <c r="AQ2" t="n">
-        <v>30.91666666666667</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>44.91739841291827</v>
+        <v>15.89297941842838</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.04368253659841</v>
+        <v>12.28082445094132</v>
       </c>
       <c r="AT2" t="n">
-        <v>28.87371587631986</v>
+        <v>3.61215496748706</v>
       </c>
       <c r="AU2" t="n">
-        <v>40.11666666666667</v>
+        <v>9.133333333333333</v>
       </c>
       <c r="AV2" t="n">
-        <v>23.43333333333333</v>
+        <v>6.283333333333333</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.68333333333334</v>
+        <v>2.85</v>
       </c>
       <c r="AX2" t="n">
-        <v>31.03077014131876</v>
+        <v>9.410558976194402</v>
       </c>
       <c r="AY2" t="n">
-        <v>16.77959665852362</v>
+        <v>7.766673171881417</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.25117348279514</v>
+        <v>1.643885804312985</v>
       </c>
       <c r="BA2" t="n">
-        <v>109.1269666666667</v>
+        <v>54.85221666666666</v>
       </c>
       <c r="BB2" t="n">
-        <v>154.5833333333333</v>
+        <v>62.6448</v>
       </c>
       <c r="BC2" t="n">
-        <v>-45.45636666666658</v>
+        <v>-7.792583333333333</v>
       </c>
       <c r="BD2" t="n">
-        <v>71.26833841096357</v>
+        <v>77.09515273421231</v>
       </c>
       <c r="BE2" t="n">
-        <v>113.8863544926646</v>
+        <v>82.2809098670003</v>
       </c>
       <c r="BF2" t="n">
-        <v>-42.61801608170103</v>
+        <v>-5.185757132787998</v>
       </c>
     </row>
     <row r="3">
@@ -952,169 +964,169 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chennai to Pondicherry</t>
+          <t>SilkBoard to Madhuravoyal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_002_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-07-2026_to_05-09-2026\PAIR_002_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>209.5919166666667</v>
+        <v>25.27086666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>221.15</v>
+        <v>20.34321666666666</v>
       </c>
       <c r="I3" t="n">
-        <v>141.62200313376</v>
+        <v>27.18076401749682</v>
       </c>
       <c r="J3" t="n">
-        <v>141.6711046862772</v>
+        <v>27.2938636578444</v>
       </c>
       <c r="K3" t="n">
-        <v>46.13817614056148</v>
+        <v>72.17266749628908</v>
       </c>
       <c r="L3" t="n">
-        <v>44.82161408578494</v>
+        <v>80.50014146258407</v>
       </c>
       <c r="M3" t="n">
-        <v>-11.55808333333331</v>
+        <v>4.927650000000011</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.04910155251721449</v>
+        <v>-0.1130996403475812</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31656205477654</v>
+        <v>-8.327473966294988</v>
       </c>
       <c r="P3" t="n">
-        <v>22.34999999999999</v>
+        <v>2.683333333333333</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>25.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.533333333333333</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.34999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3556868609874803</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1067528203067238</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2489340406807565</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.683333333333333</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.683333333333333</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.01072180369660728</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.01072180369660728</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.933333333333334</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>4.433333333333334</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.356505753799326</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1164747371577703</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.2400310166415557</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>52.5</v>
+        <v>6.766666666666667</v>
       </c>
       <c r="AP3" t="n">
-        <v>30.46666666666667</v>
+        <v>3.466666666666667</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22.03333333333333</v>
+        <v>3.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>43.39133179794914</v>
+        <v>6.807982530871882</v>
       </c>
       <c r="AS3" t="n">
-        <v>21.52228685090974</v>
+        <v>4.402529837201792</v>
       </c>
       <c r="AT3" t="n">
-        <v>21.8690449470394</v>
+        <v>2.405452693670091</v>
       </c>
       <c r="AU3" t="n">
-        <v>37.57496666666667</v>
+        <v>4.183333333333334</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="AW3" t="n">
-        <v>14.57496666666667</v>
+        <v>1.15</v>
       </c>
       <c r="AX3" t="n">
-        <v>30.28204152472709</v>
+        <v>4.29026687551903</v>
       </c>
       <c r="AY3" t="n">
-        <v>17.07262314327449</v>
+        <v>3.965547998422918</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.2094183814526</v>
+        <v>0.3247188770961116</v>
       </c>
       <c r="BA3" t="n">
-        <v>87.70028333333333</v>
+        <v>11.63753333333333</v>
       </c>
       <c r="BB3" t="n">
-        <v>134.3833333333333</v>
+        <v>13.84321666666667</v>
       </c>
       <c r="BC3" t="n">
-        <v>-46.68304999999997</v>
+        <v>-2.20568333333334</v>
       </c>
       <c r="BD3" t="n">
-        <v>67.23643719629696</v>
+        <v>16.0717928074093</v>
       </c>
       <c r="BE3" t="n">
-        <v>102.738159054381</v>
+        <v>18.92578582221969</v>
       </c>
       <c r="BF3" t="n">
-        <v>-35.50172185808404</v>
+        <v>-2.853993014810392</v>
       </c>
     </row>
     <row r="4">
@@ -1138,79 +1150,79 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chennai to Pondicherry</t>
+          <t>Madhuravoyal to SilkBoard</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_003_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\10-07-2026_to_31-07-2026\PAIR_003_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>221.5170833333333</v>
+        <v>18.67793333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>274.35</v>
+        <v>29.6565</v>
       </c>
       <c r="I4" t="n">
-        <v>148.208411945328</v>
+        <v>11.42391390088974</v>
       </c>
       <c r="J4" t="n">
-        <v>148.150219573912</v>
+        <v>11.63657856259103</v>
       </c>
       <c r="K4" t="n">
-        <v>46.35627936949886</v>
+        <v>55.44692920604529</v>
       </c>
       <c r="L4" t="n">
-        <v>43.14328255361949</v>
+        <v>59.58783215117909</v>
       </c>
       <c r="M4" t="n">
-        <v>-52.83291666666673</v>
+        <v>-10.97856666666667</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05819237141599842</v>
+        <v>-0.2126646617012895</v>
       </c>
       <c r="O4" t="n">
-        <v>3.212996815879364</v>
+        <v>-4.140902945133803</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.300000000000003</v>
+        <v>-11.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-32.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1574257220881389</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>7.266666666666667</v>
+        <v>6.55</v>
       </c>
       <c r="X4" t="n">
-        <v>13.56666666666667</v>
+        <v>18.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>-6.300000000000003</v>
+        <v>-11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.2163028850735744</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.1098089982133633</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.2993866064237053</v>
+        <v>0.1064938868602111</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1231,76 +1243,76 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.716666666666667</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.3833333333333331</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.2046142102738726</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.5759078527107181</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.3712936424368455</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>48.09223333333333</v>
+        <v>2.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>25.13333333333333</v>
+        <v>3.2872</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22.9589</v>
+        <v>-0.7871999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>38.63607021572207</v>
+        <v>2.38371396280334</v>
       </c>
       <c r="AS4" t="n">
-        <v>16.04368253659841</v>
+        <v>3.054887036688835</v>
       </c>
       <c r="AT4" t="n">
-        <v>22.59238767912366</v>
+        <v>-0.6711730738854951</v>
       </c>
       <c r="AU4" t="n">
-        <v>34.2</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="AV4" t="n">
-        <v>23.43333333333333</v>
+        <v>3.433333333333333</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.76666666666667</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="AX4" t="n">
-        <v>26.86273516629103</v>
+        <v>1.971912446606221</v>
       </c>
       <c r="AY4" t="n">
-        <v>16.77959665852362</v>
+        <v>2.822408693852921</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.08313850776741</v>
+        <v>-0.8504962472467001</v>
       </c>
       <c r="BA4" t="n">
-        <v>106.9415166666667</v>
+        <v>6.0946</v>
       </c>
       <c r="BB4" t="n">
-        <v>154.5833333333333</v>
+        <v>4.885966666666667</v>
       </c>
       <c r="BC4" t="n">
-        <v>-47.64181666666659</v>
+        <v>1.208633333333333</v>
       </c>
       <c r="BD4" t="n">
-        <v>82.12192653794388</v>
+        <v>6.851984606406608</v>
       </c>
       <c r="BE4" t="n">
-        <v>113.9111543824703</v>
+        <v>5.649473833835908</v>
       </c>
       <c r="BF4" t="n">
-        <v>-31.78922784452642</v>
+        <v>1.2025107725707</v>
       </c>
     </row>
     <row r="5">
@@ -1314,7 +1326,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1329,164 +1341,164 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_004_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026\PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>232.8915666666666</v>
+        <v>240.4436333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>269.2166666666666</v>
+        <v>274.35</v>
       </c>
       <c r="I5" t="n">
-        <v>146.1103622297162</v>
+        <v>148.1987690237775</v>
       </c>
       <c r="J5" t="n">
-        <v>146.1941703909393</v>
+        <v>148.1254196841063</v>
       </c>
       <c r="K5" t="n">
-        <v>43.31882927503337</v>
+        <v>42.80810564129094</v>
       </c>
       <c r="L5" t="n">
-        <v>44.09960930384722</v>
+        <v>44.7845362014835</v>
       </c>
       <c r="M5" t="n">
-        <v>-36.32509999999999</v>
+        <v>-33.90636666666671</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.08380816122308943</v>
+        <v>0.07334933967118218</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7807800288138438</v>
+        <v>-1.976430560192554</v>
       </c>
       <c r="P5" t="n">
-        <v>19.90823333333333</v>
+        <v>-45.40000000000001</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2440142861617139</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2440142861617139</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>29.40441666666667</v>
+        <v>25.88333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>11.26666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.13775</v>
+        <v>-43.60000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4715380269015641</v>
+        <v>0.3556868609874803</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.323446270295476</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1480917566060881</v>
+        <v>-0.4841912826215016</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.770483333333333</v>
+        <v>8.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.770483333333333</v>
+        <v>-1.799999999999999</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.003326781778833682</v>
+        <v>0.5758500319474457</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.003326781778833682</v>
+        <v>-1.222149598452762</v>
       </c>
       <c r="AI5" t="n">
         <v>8.016666666666667</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11.6</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="AK5" t="n">
-        <v>-3.583333333333332</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="AL5" t="n">
         <v>0.6265751975894123</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.005496809016533</v>
+        <v>0.5759078527107181</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.3789216114271208</v>
+        <v>0.05066734487869418</v>
       </c>
       <c r="AO5" t="n">
-        <v>55.21666666666667</v>
+        <v>55.88333333333333</v>
       </c>
       <c r="AP5" t="n">
-        <v>38.68333333333333</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.53333333333334</v>
+        <v>30.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>44.51243008835447</v>
+        <v>44.7773945763174</v>
       </c>
       <c r="AS5" t="n">
-        <v>27.60990969505806</v>
+        <v>16.04368253659841</v>
       </c>
       <c r="AT5" t="n">
-        <v>16.90252039329641</v>
+        <v>28.73371203971899</v>
       </c>
       <c r="AU5" t="n">
-        <v>38.85</v>
+        <v>40.11666666666667</v>
       </c>
       <c r="AV5" t="n">
-        <v>27.13333333333333</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="AW5" t="n">
-        <v>11.71666666666667</v>
+        <v>16.68333333333334</v>
       </c>
       <c r="AX5" t="n">
-        <v>30.69503766819436</v>
+        <v>31.03077014131876</v>
       </c>
       <c r="AY5" t="n">
-        <v>19.99447365781878</v>
+        <v>16.77959665852362</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.70056401037558</v>
+        <v>14.25117348279514</v>
       </c>
       <c r="BA5" t="n">
-        <v>99.63333333333334</v>
+        <v>102.3936333333333</v>
       </c>
       <c r="BB5" t="n">
-        <v>120.7166666666667</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="BC5" t="n">
-        <v>-21.08333333333336</v>
+        <v>-42.2397</v>
       </c>
       <c r="BD5" t="n">
-        <v>69.80145446689757</v>
+        <v>70.83249221561701</v>
       </c>
       <c r="BE5" t="n">
-        <v>97.0168296725888</v>
+        <v>112.0883548622644</v>
       </c>
       <c r="BF5" t="n">
-        <v>-27.21537520569123</v>
+        <v>-41.25586264664739</v>
       </c>
     </row>
     <row r="6">
@@ -1515,164 +1527,164 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>199.7801333333333</v>
+        <v>209.5919166666667</v>
       </c>
       <c r="H6" t="n">
-        <v>272.7087666666667</v>
+        <v>221.15</v>
       </c>
       <c r="I6" t="n">
-        <v>147.8063808897662</v>
+        <v>141.62200313376</v>
       </c>
       <c r="J6" t="n">
-        <v>147.7347082243865</v>
+        <v>141.6711046862772</v>
       </c>
       <c r="K6" t="n">
-        <v>47.1164527446597</v>
+        <v>47.25384199133067</v>
       </c>
       <c r="L6" t="n">
-        <v>43.36902945799262</v>
+        <v>44.82161408578494</v>
       </c>
       <c r="M6" t="n">
-        <v>-72.92863333333338</v>
+        <v>-11.55808333333331</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07167266537967976</v>
+        <v>-0.04910155251721449</v>
       </c>
       <c r="O6" t="n">
-        <v>3.747423286667086</v>
+        <v>2.43222790554573</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.53333333333334</v>
+        <v>-0.9833333333333378</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>12.03333333333333</v>
+        <v>25.88333333333333</v>
       </c>
       <c r="X6" t="n">
-        <v>13.56666666666667</v>
+        <v>31.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.53333333333334</v>
+        <v>-5.916666666666671</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3736603870816042</v>
+        <v>0.3556868609874803</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.1893981680228127</v>
+        <v>0.1341259604332779</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.933333333333334</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>4.933333333333334</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.4693593484285414</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>0.4693593484285414</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.933333333333334</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.266666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>-1.266666666666667</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>0.356505753799326</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.4655888960075587</v>
+        <v>0.1164747371577703</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.4655888960075587</v>
+        <v>0.2400310166415557</v>
       </c>
       <c r="AO6" t="n">
-        <v>46.9</v>
+        <v>52.33333333333334</v>
       </c>
       <c r="AP6" t="n">
-        <v>25.12543333333333</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21.77456666666667</v>
+        <v>21.86666666666667</v>
       </c>
       <c r="AR6" t="n">
-        <v>37.60735272104981</v>
+        <v>43.25132796134825</v>
       </c>
       <c r="AS6" t="n">
-        <v>16.04658812968748</v>
+        <v>21.52228685090974</v>
       </c>
       <c r="AT6" t="n">
-        <v>21.56076459136233</v>
+        <v>21.72904111043851</v>
       </c>
       <c r="AU6" t="n">
-        <v>35.55</v>
+        <v>37.57496666666667</v>
       </c>
       <c r="AV6" t="n">
-        <v>23.43333333333333</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>12.11666666666667</v>
+        <v>14.57496666666667</v>
       </c>
       <c r="AX6" t="n">
-        <v>27.61065850344794</v>
+        <v>30.28204152472709</v>
       </c>
       <c r="AY6" t="n">
-        <v>16.77959665852362</v>
+        <v>17.07262314327449</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10.83106184492432</v>
+        <v>13.2094183814526</v>
       </c>
       <c r="BA6" t="n">
-        <v>105.2968</v>
+        <v>82.93361666666667</v>
       </c>
       <c r="BB6" t="n">
-        <v>153.4</v>
+        <v>134.3833333333333</v>
       </c>
       <c r="BC6" t="n">
-        <v>-48.1032</v>
+        <v>-51.44971666666663</v>
       </c>
       <c r="BD6" t="n">
-        <v>82.21470927818682</v>
+        <v>66.9070816844693</v>
       </c>
       <c r="BE6" t="n">
-        <v>113.6030563965588</v>
+        <v>102.738159054381</v>
       </c>
       <c r="BF6" t="n">
-        <v>-31.38834711837198</v>
+        <v>-35.8310773699117</v>
       </c>
     </row>
     <row r="7">
@@ -1686,7 +1698,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1696,169 +1708,169 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pondicherry to Chennai</t>
+          <t>Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_006_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_006_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>241.37365</v>
+        <v>221.5170833333333</v>
       </c>
       <c r="H7" t="n">
-        <v>241.6157666666667</v>
+        <v>274.35</v>
       </c>
       <c r="I7" t="n">
-        <v>143.678327457659</v>
+        <v>148.208411945328</v>
       </c>
       <c r="J7" t="n">
-        <v>143.7061031155876</v>
+        <v>148.150219573912</v>
       </c>
       <c r="K7" t="n">
-        <v>43.15630919960726</v>
+        <v>49.30661820086556</v>
       </c>
       <c r="L7" t="n">
-        <v>42.008597388821</v>
+        <v>44.79217019920052</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2421166666667034</v>
+        <v>-52.83291666666673</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02777565792860059</v>
+        <v>0.05819237141599842</v>
       </c>
       <c r="O7" t="n">
-        <v>1.147711810786255</v>
+        <v>4.514448001665038</v>
       </c>
       <c r="P7" t="n">
-        <v>29.43553333333333</v>
+        <v>-34.95848333333333</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>42.53553333333333</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="X7" t="n">
-        <v>13.1</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>29.43553333333333</v>
+        <v>-39.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6596733987548126</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3335967503409809</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3260766484138317</v>
+        <v>-0.4568123285118442</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>14.29151666666667</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>4.341516666666671</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.33611605697715</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>0.5381164265769423</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.616666666666667</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.483333333333333</v>
+        <v>0.3833333333333331</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.4394311316082445</v>
+        <v>0.2046142102738726</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.270112055303145</v>
+        <v>0.5759078527107181</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.1693190763050995</v>
+        <v>-0.3712936424368455</v>
       </c>
       <c r="AO7" t="n">
-        <v>52.5</v>
+        <v>48.09223333333333</v>
       </c>
       <c r="AP7" t="n">
-        <v>43.73333333333333</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.766666666666673</v>
+        <v>22.9589</v>
       </c>
       <c r="AR7" t="n">
-        <v>42.76805623685773</v>
+        <v>38.63607021572207</v>
       </c>
       <c r="AS7" t="n">
-        <v>31.25618145550666</v>
+        <v>16.04368253659841</v>
       </c>
       <c r="AT7" t="n">
-        <v>11.51187478135107</v>
+        <v>22.59238767912366</v>
       </c>
       <c r="AU7" t="n">
-        <v>38.05478333333333</v>
+        <v>33.45</v>
       </c>
       <c r="AV7" t="n">
-        <v>34.95</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.10478333333333</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="AX7" t="n">
-        <v>30.13874197108473</v>
+        <v>26.28668300273065</v>
       </c>
       <c r="AY7" t="n">
-        <v>25.11354425718663</v>
+        <v>16.77959665852362</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.025197713898102</v>
+        <v>9.507086344207032</v>
       </c>
       <c r="BA7" t="n">
-        <v>104.1833333333333</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>124.3324333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="BC7" t="n">
-        <v>-20.1491</v>
+        <v>-51.23333333333329</v>
       </c>
       <c r="BD7" t="n">
-        <v>69.67242471935344</v>
+        <v>80.36186264452711</v>
       </c>
       <c r="BE7" t="n">
-        <v>86.63218730858281</v>
+        <v>112.1131547520701</v>
       </c>
       <c r="BF7" t="n">
-        <v>-16.95976258922937</v>
+        <v>-31.75129210754299</v>
       </c>
     </row>
     <row r="8">
@@ -1882,169 +1894,169 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pondicherry to Chennai</t>
+          <t>Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_007_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_007_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>171.54615</v>
+        <v>232.8915666666666</v>
       </c>
       <c r="H8" t="n">
-        <v>188.0674333333333</v>
+        <v>269.2166666666666</v>
       </c>
       <c r="I8" t="n">
-        <v>126.503272181271</v>
+        <v>146.1103622297162</v>
       </c>
       <c r="J8" t="n">
-        <v>126.4504264596244</v>
+        <v>146.1941703909393</v>
       </c>
       <c r="K8" t="n">
-        <v>51.80910898442515</v>
+        <v>44.76153869689547</v>
       </c>
       <c r="L8" t="n">
-        <v>46.12090225545156</v>
+        <v>44.84902776787012</v>
       </c>
       <c r="M8" t="n">
-        <v>-16.52128333333329</v>
+        <v>-36.32509999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05284572164660517</v>
+        <v>-0.08380816122308943</v>
       </c>
       <c r="O8" t="n">
-        <v>5.68820672897359</v>
+        <v>-0.08748907097464809</v>
       </c>
       <c r="P8" t="n">
-        <v>25.41886666666667</v>
+        <v>-36.49176666666666</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>25.41886666666667</v>
+        <v>29.40441666666667</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="Y8" t="n">
-        <v>25.41886666666667</v>
+        <v>-41.67891666666666</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3245330510269857</v>
+        <v>0.4715380269015641</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>0.56746055645719</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3245330510269857</v>
+        <v>-0.09592252955562586</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>9.237150000000002</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>5.187150000000002</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.7233426716155921</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>0.1707796029244358</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>8.016666666666667</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.3</v>
+        <v>11.6</v>
       </c>
       <c r="AK8" t="n">
-        <v>-2.3</v>
+        <v>-3.583333333333332</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>0.6265751975894123</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.2122753364088935</v>
+        <v>1.005496809016533</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.2122753364088935</v>
+        <v>-0.3789216114271208</v>
       </c>
       <c r="AO8" t="n">
-        <v>43.56666666666667</v>
+        <v>55.05</v>
       </c>
       <c r="AP8" t="n">
-        <v>45.5</v>
+        <v>38.68333333333333</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.93333333333333</v>
+        <v>16.36666666666667</v>
       </c>
       <c r="AR8" t="n">
-        <v>38.51537746372311</v>
+        <v>44.37242625175359</v>
       </c>
       <c r="AS8" t="n">
-        <v>34.12509917533455</v>
+        <v>27.60990969505806</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.390278288388565</v>
+        <v>16.76251655669553</v>
       </c>
       <c r="AU8" t="n">
-        <v>32.13333333333333</v>
+        <v>38.85</v>
       </c>
       <c r="AV8" t="n">
-        <v>29.80076666666667</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.332566666666661</v>
+        <v>12.03333333333333</v>
       </c>
       <c r="AX8" t="n">
-        <v>27.33010874041363</v>
+        <v>30.69503766819436</v>
       </c>
       <c r="AY8" t="n">
-        <v>22.73451919053936</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.595589549874269</v>
+        <v>10.80210939628688</v>
       </c>
       <c r="BA8" t="n">
-        <v>70.42728333333334</v>
+        <v>92.33333333333333</v>
       </c>
       <c r="BB8" t="n">
-        <v>86.75</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="BC8" t="n">
-        <v>-16.32271666666666</v>
+        <v>-24.64999999999998</v>
       </c>
       <c r="BD8" t="n">
-        <v>60.33325292610726</v>
+        <v>69.22144241366169</v>
       </c>
       <c r="BE8" t="n">
-        <v>69.26153371508154</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="BF8" t="n">
-        <v>-8.928280788974284</v>
+        <v>-27.34436957614724</v>
       </c>
     </row>
     <row r="9">
@@ -2068,169 +2080,169 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pondicherry to Chennai</t>
+          <t>Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_008_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>183.89555</v>
+        <v>199.7801333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>180.3055833333333</v>
+        <v>272.7087666666667</v>
       </c>
       <c r="I9" t="n">
-        <v>126.6046070482763</v>
+        <v>147.8063808897662</v>
       </c>
       <c r="J9" t="n">
-        <v>126.5641866441461</v>
+        <v>147.7347082243865</v>
       </c>
       <c r="K9" t="n">
-        <v>46.70774678068461</v>
+        <v>48.10943109063845</v>
       </c>
       <c r="L9" t="n">
-        <v>49.76956595619203</v>
+        <v>45.04354059322232</v>
       </c>
       <c r="M9" t="n">
-        <v>3.589966666666697</v>
+        <v>-72.92863333333338</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04042040413020231</v>
+        <v>0.07167266537967976</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.061819175507424</v>
+        <v>3.065890497416135</v>
       </c>
       <c r="P9" t="n">
-        <v>17.46666666666666</v>
+        <v>-62.65000000000001</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>21.48333333333333</v>
+        <v>12.03333333333333</v>
       </c>
       <c r="X9" t="n">
-        <v>4.1</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.38333333333333</v>
+        <v>-57.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.237667416199215</v>
+        <v>0.3736603870816042</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1135008893025534</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1241665268966616</v>
+        <v>-0.4662177565273777</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.08333333333333333</v>
+        <v>4.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.08333333333333333</v>
+        <v>-5.199999999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.7015215125621636</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-1.096478117838044</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.683333333333333</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.35</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.333333333333333</v>
+        <v>-1.266666666666667</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.3011879778687425</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.1671868728596241</v>
+        <v>0.4655888960075587</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.1340011050091184</v>
+        <v>-0.4655888960075587</v>
       </c>
       <c r="AO9" t="n">
-        <v>48.81666666666667</v>
+        <v>46.9</v>
       </c>
       <c r="AP9" t="n">
-        <v>35.28333333333333</v>
+        <v>25.12543333333333</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.53333333333334</v>
+        <v>21.77456666666667</v>
       </c>
       <c r="AR9" t="n">
-        <v>38.82861695950649</v>
+        <v>37.60735272104981</v>
       </c>
       <c r="AS9" t="n">
-        <v>26.65829138970381</v>
+        <v>16.04658812968748</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.17032556980268</v>
+        <v>21.56076459136233</v>
       </c>
       <c r="AU9" t="n">
-        <v>35.46666666666667</v>
+        <v>35.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>27.01666666666667</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.449999999999999</v>
+        <v>12.11666666666667</v>
       </c>
       <c r="AX9" t="n">
-        <v>27.95827681357427</v>
+        <v>27.61065850344794</v>
       </c>
       <c r="AY9" t="n">
-        <v>21.58020657782552</v>
+        <v>16.77959665852362</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.378070235748748</v>
+        <v>10.83106184492432</v>
       </c>
       <c r="BA9" t="n">
-        <v>76.36221666666667</v>
+        <v>100.5468</v>
       </c>
       <c r="BB9" t="n">
-        <v>89.67225000000001</v>
+        <v>143.45</v>
       </c>
       <c r="BC9" t="n">
-        <v>-13.31003333333334</v>
+        <v>-42.90319999999998</v>
       </c>
       <c r="BD9" t="n">
-        <v>59.27885788112761</v>
+        <v>81.51318776562465</v>
       </c>
       <c r="BE9" t="n">
-        <v>77.94451962578719</v>
+        <v>111.8050567661586</v>
       </c>
       <c r="BF9" t="n">
-        <v>-18.66566174465959</v>
+        <v>-30.29186900053395</v>
       </c>
     </row>
     <row r="10">
@@ -2254,169 +2266,169 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pondicherry to Chennai</t>
+          <t>Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_009_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_25-09-2026\PAIR_009_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>205.7538833333333</v>
+        <v>247.26765</v>
       </c>
       <c r="H10" t="n">
-        <v>194.9584</v>
+        <v>274.35</v>
       </c>
       <c r="I10" t="n">
-        <v>123.9185956857711</v>
+        <v>148.4081122812309</v>
       </c>
       <c r="J10" t="n">
-        <v>123.941936072907</v>
+        <v>148.1693420519742</v>
       </c>
       <c r="K10" t="n">
-        <v>43.25878919401418</v>
+        <v>47.63775321159345</v>
       </c>
       <c r="L10" t="n">
-        <v>42.80552488152868</v>
+        <v>44.79805655414056</v>
       </c>
       <c r="M10" t="n">
-        <v>10.79548333333329</v>
+        <v>-27.08235000000002</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02334038713590303</v>
+        <v>0.2387702292566871</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4532643124854943</v>
+        <v>2.83969665745289</v>
       </c>
       <c r="P10" t="n">
-        <v>34.55</v>
+        <v>-17.70095000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>34.55</v>
+        <v>35.56666666666667</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>34.55</v>
+        <v>-33.91666666666666</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.4840507138833688</v>
+        <v>0.5933262321891101</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.4840507138833688</v>
+        <v>-0.2465519114198719</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>26.16571666666666</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>16.21571666666666</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>0.5067319571443681</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-1.29126767325584</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.1</v>
+        <v>2.05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.1</v>
+        <v>0.3333333333333328</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.4394311316082445</v>
+        <v>0.1799078409944621</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>0.5759078527107181</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.4394311316082445</v>
+        <v>-0.396000011716256</v>
       </c>
       <c r="AO10" t="n">
-        <v>44.28333333333333</v>
+        <v>63.03526666666667</v>
       </c>
       <c r="AP10" t="n">
-        <v>39.51666666666667</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.766666666666659</v>
+        <v>37.90193333333335</v>
       </c>
       <c r="AR10" t="n">
-        <v>35.86032280254005</v>
+        <v>45.7896379485424</v>
       </c>
       <c r="AS10" t="n">
-        <v>28.52077529734963</v>
+        <v>16.04368253659841</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.339547505190417</v>
+        <v>29.74595541194399</v>
       </c>
       <c r="AU10" t="n">
-        <v>31.8</v>
+        <v>45.45</v>
       </c>
       <c r="AV10" t="n">
-        <v>30.8</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="AW10" t="n">
-        <v>1</v>
+        <v>22.01666666666667</v>
       </c>
       <c r="AX10" t="n">
-        <v>25.29976226838916</v>
+        <v>33.36307095293761</v>
       </c>
       <c r="AY10" t="n">
-        <v>21.13389550628888</v>
+        <v>16.77959665852362</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.165866762100279</v>
+        <v>16.58347429441399</v>
       </c>
       <c r="BA10" t="n">
-        <v>91.02055</v>
+        <v>75</v>
       </c>
       <c r="BB10" t="n">
-        <v>103.2584</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="BC10" t="n">
-        <v>-12.23784999999999</v>
+        <v>-69.6333333333333</v>
       </c>
       <c r="BD10" t="n">
-        <v>61.83502876935029</v>
+        <v>67.97543734942298</v>
       </c>
       <c r="BE10" t="n">
-        <v>74.17819311324479</v>
+        <v>112.1322772301322</v>
       </c>
       <c r="BF10" t="n">
-        <v>-12.3431643438945</v>
+        <v>-44.15683988070923</v>
       </c>
     </row>
     <row r="11">
@@ -2430,7 +2442,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2445,164 +2457,164 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_010_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_010_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>223.0419833333333</v>
+        <v>241.37365</v>
       </c>
       <c r="H11" t="n">
         <v>241.6157666666667</v>
       </c>
       <c r="I11" t="n">
-        <v>143.715559613142</v>
+        <v>143.678327457659</v>
       </c>
       <c r="J11" t="n">
-        <v>143.7030109884508</v>
+        <v>143.7061031155876</v>
       </c>
       <c r="K11" t="n">
-        <v>45.56809333466344</v>
+        <v>44.63387255371435</v>
       </c>
       <c r="L11" t="n">
-        <v>42.0076907503904</v>
+        <v>42.34188357413701</v>
       </c>
       <c r="M11" t="n">
-        <v>-18.57378333333341</v>
+        <v>-0.2421166666667034</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01254862469119189</v>
+        <v>-0.02777565792860059</v>
       </c>
       <c r="O11" t="n">
-        <v>3.560402584273035</v>
+        <v>2.29198897957734</v>
       </c>
       <c r="P11" t="n">
-        <v>21.39703333333333</v>
+        <v>9.552200000000013</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>34.49703333333333</v>
+        <v>43.48553333333334</v>
       </c>
       <c r="X11" t="n">
-        <v>13.1</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="Y11" t="n">
-        <v>21.39703333333333</v>
+        <v>6.502200000000016</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.521661623484558</v>
+        <v>1.332101358262426</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3335967503409809</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1880648731435771</v>
+        <v>0.8980233192540306</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.7541054091629448</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.038955216433607</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-1.284849807270662</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.266666666666667</v>
+        <v>4.1</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.616666666666667</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.649999999999999</v>
+        <v>2.483333333333333</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.3548232692194973</v>
+        <v>0.4394311316082445</v>
       </c>
       <c r="AM11" t="n">
         <v>0.270112055303145</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.08471121391635228</v>
+        <v>0.1693190763050995</v>
       </c>
       <c r="AO11" t="n">
-        <v>54.2</v>
+        <v>52.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>43.73333333333333</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.46666666666668</v>
+        <v>10.06666666666667</v>
       </c>
       <c r="AR11" t="n">
-        <v>43.32090510862054</v>
+        <v>42.76805623685773</v>
       </c>
       <c r="AS11" t="n">
-        <v>31.2545285587253</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AT11" t="n">
-        <v>12.06637654989524</v>
+        <v>12.17007709217261</v>
       </c>
       <c r="AU11" t="n">
-        <v>35.34495</v>
+        <v>37.47145</v>
       </c>
       <c r="AV11" t="n">
         <v>34.95</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.3949499999999944</v>
+        <v>2.521449999999994</v>
       </c>
       <c r="AX11" t="n">
-        <v>28.54498304892895</v>
+        <v>29.77502417243205</v>
       </c>
       <c r="AY11" t="n">
         <v>25.11354425718663</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.431438791742323</v>
+        <v>4.661479915245422</v>
       </c>
       <c r="BA11" t="n">
-        <v>93.73333333333333</v>
+        <v>96.26666666666667</v>
       </c>
       <c r="BB11" t="n">
-        <v>124.3324333333333</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="BC11" t="n">
-        <v>-30.59909999999996</v>
+        <v>-24.86576666666663</v>
       </c>
       <c r="BD11" t="n">
-        <v>70.9731865628885</v>
+        <v>68.60960914933557</v>
       </c>
       <c r="BE11" t="n">
-        <v>86.63074807822738</v>
+        <v>85.25143440297076</v>
       </c>
       <c r="BF11" t="n">
-        <v>-15.65756151533888</v>
+        <v>-16.64182525363519</v>
       </c>
     </row>
     <row r="12">
@@ -2616,7 +2628,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2626,169 +2638,169 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chennai to Pondicherry</t>
+          <t>Pondicherry to Chennai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_011_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_011_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>205.6434166666667</v>
+        <v>171.54615</v>
       </c>
       <c r="H12" t="n">
-        <v>221.15</v>
+        <v>188.0674333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>141.5990549680233</v>
+        <v>126.503272181271</v>
       </c>
       <c r="J12" t="n">
-        <v>141.6663057069586</v>
+        <v>126.4504264596244</v>
       </c>
       <c r="K12" t="n">
-        <v>48.28995397818726</v>
+        <v>51.96681218238075</v>
       </c>
       <c r="L12" t="n">
-        <v>44.82009341634151</v>
+        <v>46.52364975832732</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.50658333333331</v>
+        <v>-16.52128333333329</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0672507389353143</v>
+        <v>0.05284572164660517</v>
       </c>
       <c r="O12" t="n">
-        <v>3.469860561845756</v>
+        <v>5.443162424053426</v>
       </c>
       <c r="P12" t="n">
-        <v>3.733333333333333</v>
+        <v>0.9188666666666663</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.349999999999998</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0045857861689476</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>7.266666666666667</v>
+        <v>26.36886666666667</v>
       </c>
       <c r="X12" t="n">
-        <v>3.533333333333333</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.733333333333333</v>
+        <v>2.652200000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.9969610105345994</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1569191283739878</v>
+        <v>0.8799619682745543</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>-1.733333333333333</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.3292747005187303</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>0.7448250731105075</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0.4155503725917772</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.6000000000000001</v>
+        <v>-1.3</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.2046142102738726</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.1164747371577703</v>
+        <v>0.1079082363261396</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0881394731161023</v>
+        <v>-0.1079082363261396</v>
       </c>
       <c r="AO12" t="n">
-        <v>43.83333333333334</v>
+        <v>43.56666666666667</v>
       </c>
       <c r="AP12" t="n">
-        <v>30.46666666666667</v>
+        <v>45.08333333333334</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.36666666666667</v>
+        <v>-1.516666666666673</v>
       </c>
       <c r="AR12" t="n">
-        <v>36.80847059423598</v>
+        <v>38.51537746372311</v>
       </c>
       <c r="AS12" t="n">
-        <v>21.52025885865341</v>
+        <v>33.88390179261686</v>
       </c>
       <c r="AT12" t="n">
-        <v>15.28821173558257</v>
+        <v>4.631475671106251</v>
       </c>
       <c r="AU12" t="n">
-        <v>30.75</v>
+        <v>31.55</v>
       </c>
       <c r="AV12" t="n">
-        <v>23</v>
+        <v>29.80076666666667</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.75</v>
+        <v>1.749233333333329</v>
       </c>
       <c r="AX12" t="n">
-        <v>25.36797775428393</v>
+        <v>26.96639094176094</v>
       </c>
       <c r="AY12" t="n">
-        <v>17.06985215621225</v>
+        <v>22.73451919053936</v>
       </c>
       <c r="AZ12" t="n">
-        <v>8.298125598071682</v>
+        <v>4.231871751221583</v>
       </c>
       <c r="BA12" t="n">
-        <v>98.77674999999999</v>
+        <v>69.41061666666666</v>
       </c>
       <c r="BB12" t="n">
-        <v>134.3833333333333</v>
+        <v>85.78333333333333</v>
       </c>
       <c r="BC12" t="n">
-        <v>-35.6065833333333</v>
+        <v>-16.37271666666668</v>
       </c>
       <c r="BD12" t="n">
-        <v>78.83492659413233</v>
+        <v>59.6952680647336</v>
       </c>
       <c r="BE12" t="n">
-        <v>102.738159054381</v>
+        <v>68.86227312477148</v>
       </c>
       <c r="BF12" t="n">
-        <v>-23.90323246024867</v>
+        <v>-9.16700506003788</v>
       </c>
     </row>
     <row r="13">
@@ -2812,169 +2824,169 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chennai to Pondicherry</t>
+          <t>Pondicherry to Chennai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_012_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>219.9365833333333</v>
+        <v>183.89555</v>
       </c>
       <c r="H13" t="n">
-        <v>269.2166666666666</v>
+        <v>180.3055833333333</v>
       </c>
       <c r="I13" t="n">
-        <v>146.1177802267258</v>
+        <v>126.6046070482763</v>
       </c>
       <c r="J13" t="n">
-        <v>146.2265476173816</v>
+        <v>126.5641866441461</v>
       </c>
       <c r="K13" t="n">
-        <v>46.08133386225383</v>
+        <v>48.84353918109128</v>
       </c>
       <c r="L13" t="n">
-        <v>44.10804715430679</v>
+        <v>49.97551623726486</v>
       </c>
       <c r="M13" t="n">
-        <v>-49.28008333333329</v>
+        <v>3.589966666666697</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1087673906557995</v>
+        <v>0.04042040413020231</v>
       </c>
       <c r="O13" t="n">
-        <v>1.97328670794704</v>
+        <v>-1.131977056173582</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.000000000000003</v>
+        <v>-0.6631</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-36.9</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2485278553085821</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1291339888921559</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>7.266666666666667</v>
+        <v>21.48333333333333</v>
       </c>
       <c r="X13" t="n">
-        <v>11.26666666666667</v>
+        <v>27.98333333333333</v>
       </c>
       <c r="Y13" t="n">
-        <v>-4.000000000000003</v>
+        <v>-6.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.237667416199215</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.323446270295476</v>
+        <v>0.2139821779699679</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.05977432161476443</v>
+        <v>0.02368523822924709</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>8.303566666666667</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>5.8369</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>0.9134082250757436</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.531702164179549</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0.6182939391038054</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.233333333333333</v>
+        <v>1.683333333333333</v>
       </c>
       <c r="AJ13" t="n">
-        <v>11.6</v>
+        <v>0.35</v>
       </c>
       <c r="AK13" t="n">
-        <v>-7.366666666666666</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.2739207603422623</v>
+        <v>0.3011879778687425</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.033360466311896</v>
+        <v>0.1671868728596241</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.7594397059696337</v>
+        <v>0.1340011050091184</v>
       </c>
       <c r="AO13" t="n">
-        <v>46.35</v>
+        <v>48.81666666666667</v>
       </c>
       <c r="AP13" t="n">
-        <v>38.68333333333333</v>
+        <v>34.15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.666666666666671</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="AR13" t="n">
-        <v>38.07535235688084</v>
+        <v>38.82861695950649</v>
       </c>
       <c r="AS13" t="n">
-        <v>27.60990969505806</v>
+        <v>26.10973756311647</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.46544266182278</v>
+        <v>12.71887939639002</v>
       </c>
       <c r="AU13" t="n">
-        <v>32.55325</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="AV13" t="n">
-        <v>27.13333333333333</v>
+        <v>27.01666666666667</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.419916666666669</v>
+        <v>8.116666666666664</v>
       </c>
       <c r="AX13" t="n">
-        <v>26.21191049416226</v>
+        <v>27.71428406489335</v>
       </c>
       <c r="AY13" t="n">
-        <v>19.99447365781878</v>
+        <v>21.58020657782552</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.217436836343481</v>
+        <v>6.134077487067827</v>
       </c>
       <c r="BA13" t="n">
-        <v>106.6166666666667</v>
+        <v>68.47531666666667</v>
       </c>
       <c r="BB13" t="n">
-        <v>120.7166666666667</v>
+        <v>88.33891666666666</v>
       </c>
       <c r="BC13" t="n">
-        <v>-14.09999999999999</v>
+        <v>-19.86359999999999</v>
       </c>
       <c r="BD13" t="n">
-        <v>81.17353080024326</v>
+        <v>58.60944240473279</v>
       </c>
       <c r="BE13" t="n">
-        <v>97.0168296725888</v>
+        <v>76.961371288195</v>
       </c>
       <c r="BF13" t="n">
-        <v>-15.84329887234554</v>
+        <v>-18.35192888346221</v>
       </c>
     </row>
     <row r="14">
@@ -2998,169 +3010,169 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chennai to Pondicherry</t>
+          <t>Pondicherry to Chennai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_013_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>186.11555</v>
+        <v>205.7538833333333</v>
       </c>
       <c r="H14" t="n">
-        <v>221.15</v>
+        <v>194.9584</v>
       </c>
       <c r="I14" t="n">
-        <v>141.7178099447946</v>
+        <v>123.9185956857711</v>
       </c>
       <c r="J14" t="n">
-        <v>141.7137294264382</v>
+        <v>123.941936072907</v>
       </c>
       <c r="K14" t="n">
-        <v>47.90276473827162</v>
+        <v>44.92387297676966</v>
       </c>
       <c r="L14" t="n">
-        <v>44.83512073701105</v>
+        <v>42.76203218085404</v>
       </c>
       <c r="M14" t="n">
-        <v>-35.03444999999999</v>
+        <v>10.79548333333329</v>
       </c>
       <c r="N14" t="n">
-        <v>0.004080518356403218</v>
+        <v>-0.02334038713590303</v>
       </c>
       <c r="O14" t="n">
-        <v>3.067644001260568</v>
+        <v>2.161840795915616</v>
       </c>
       <c r="P14" t="n">
-        <v>5.4</v>
+        <v>20.1</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>8.933333333333334</v>
+        <v>35.5</v>
       </c>
       <c r="X14" t="n">
-        <v>3.533333333333333</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.4</v>
+        <v>14.11666666666667</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.2591759316479205</v>
+        <v>1.156478673390982</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.1524231113411967</v>
+        <v>1.04740651736726</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>6.983333333333333</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>5.983333333333333</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>0.5163595282581407</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.8385213433327759</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>-0.3221618150746353</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-1.5</v>
+        <v>4.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>0.4394311316082445</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.1164747371577703</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.1164747371577703</v>
+        <v>0.4394311316082445</v>
       </c>
       <c r="AO14" t="n">
-        <v>45.23761666666667</v>
+        <v>44.28333333333333</v>
       </c>
       <c r="AP14" t="n">
+        <v>39.18333333333333</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>35.86032280254005</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>28.21320161975721</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.647121182782836</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>31.21666666666667</v>
+      </c>
+      <c r="AV14" t="n">
         <v>30.46666666666667</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>14.77095</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>36.81108423008403</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>21.5632715446163</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>15.24781268546773</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>34.96666666666667</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>23</v>
-      </c>
       <c r="AW14" t="n">
-        <v>11.96666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="AX14" t="n">
-        <v>27.29337511764809</v>
+        <v>24.93604446973648</v>
       </c>
       <c r="AY14" t="n">
-        <v>17.07426318972899</v>
+        <v>20.93633895165053</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10.2191119279191</v>
+        <v>3.99970551808595</v>
       </c>
       <c r="BA14" t="n">
-        <v>96.97793333333334</v>
+        <v>83.67055000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>134.3833333333333</v>
+        <v>102.9250666666667</v>
       </c>
       <c r="BC14" t="n">
-        <v>-37.40539999999996</v>
+        <v>-19.25451666666669</v>
       </c>
       <c r="BD14" t="n">
-        <v>77.35417466541456</v>
+        <v>61.00995908023722</v>
       </c>
       <c r="BE14" t="n">
-        <v>102.738159054381</v>
+        <v>73.8448020021428</v>
       </c>
       <c r="BF14" t="n">
-        <v>-25.38398438896644</v>
+        <v>-12.83484292190558</v>
       </c>
     </row>
     <row r="15">
@@ -3174,7 +3186,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3189,164 +3201,164 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_014_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>184.8726166666667</v>
+        <v>223.0419833333333</v>
       </c>
       <c r="H15" t="n">
-        <v>189.8237333333333</v>
+        <v>241.6157666666667</v>
       </c>
       <c r="I15" t="n">
-        <v>126.797111280885</v>
+        <v>143.715559613142</v>
       </c>
       <c r="J15" t="n">
-        <v>126.7676219192398</v>
+        <v>143.7030109884508</v>
       </c>
       <c r="K15" t="n">
-        <v>46.49901997986691</v>
+        <v>46.2946098216972</v>
       </c>
       <c r="L15" t="n">
-        <v>45.74782714011837</v>
+        <v>42.3414520907443</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.951116666666621</v>
+        <v>-18.57378333333341</v>
       </c>
       <c r="N15" t="n">
-        <v>0.02948936164520433</v>
+        <v>0.01254862469119189</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7511928397485406</v>
+        <v>3.953157730952903</v>
       </c>
       <c r="P15" t="n">
-        <v>21.56666666666666</v>
+        <v>-3.30296666666667</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>21.48333333333333</v>
+        <v>34.49703333333333</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="Y15" t="n">
-        <v>21.48333333333333</v>
+        <v>-2.4863</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.237667416199215</v>
+        <v>0.521661623484558</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.237667416199215</v>
+        <v>0.0875835844761626</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.08333333333333333</v>
+        <v>3.683333333333333</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.08333333333333333</v>
+        <v>-0.8166666666666669</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.5589577464659954</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.037302319652247</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-1.478344573186251</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.683333333333333</v>
+        <v>5.266666666666667</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.633333333333333</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.95</v>
+        <v>3.649999999999999</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.3011879778687425</v>
+        <v>0.3548232692194973</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.2267712765180789</v>
+        <v>0.270112055303145</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.07441670135066361</v>
+        <v>0.08471121391635228</v>
       </c>
       <c r="AO15" t="n">
-        <v>48.91905</v>
+        <v>54.2</v>
       </c>
       <c r="AP15" t="n">
-        <v>45.67373333333333</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.245316666666668</v>
+        <v>11.76666666666667</v>
       </c>
       <c r="AR15" t="n">
-        <v>38.90083595250158</v>
+        <v>43.32090510862054</v>
       </c>
       <c r="AS15" t="n">
-        <v>34.23732716182031</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.66350879068127</v>
+        <v>12.72292596393542</v>
       </c>
       <c r="AU15" t="n">
-        <v>35.46666666666667</v>
+        <v>34.92828333333333</v>
       </c>
       <c r="AV15" t="n">
-        <v>29.9</v>
+        <v>34.95</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.56666666666667</v>
+        <v>-0.02171666666666994</v>
       </c>
       <c r="AX15" t="n">
-        <v>27.95827681357427</v>
+        <v>28.28601681705657</v>
       </c>
       <c r="AY15" t="n">
-        <v>22.79241179514765</v>
+        <v>25.11354425718663</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.165865018426619</v>
+        <v>3.172472559869941</v>
       </c>
       <c r="BA15" t="n">
-        <v>77.23690000000001</v>
+        <v>90.46666666666667</v>
       </c>
       <c r="BB15" t="n">
-        <v>87.90000000000001</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="BC15" t="n">
-        <v>-10.6631</v>
+        <v>-30.66576666666663</v>
       </c>
       <c r="BD15" t="n">
-        <v>59.39914312074116</v>
+        <v>70.67319504829489</v>
       </c>
       <c r="BE15" t="n">
-        <v>69.39411264349368</v>
+        <v>85.24999517261531</v>
       </c>
       <c r="BF15" t="n">
-        <v>-9.994969522752527</v>
+        <v>-14.57680012432043</v>
       </c>
     </row>
     <row r="16">
@@ -3375,164 +3387,164 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>139.3205333333333</v>
+        <v>72.03223333333334</v>
       </c>
       <c r="H16" t="n">
-        <v>149.51085</v>
+        <v>78.34408333333334</v>
       </c>
       <c r="I16" t="n">
-        <v>106.7510397234517</v>
+        <v>44.14952488525887</v>
       </c>
       <c r="J16" t="n">
-        <v>106.7303536725813</v>
+        <v>44.09816148211158</v>
       </c>
       <c r="K16" t="n">
-        <v>51.59099322590557</v>
+        <v>49.19356496670422</v>
       </c>
       <c r="L16" t="n">
-        <v>49.9289852595555</v>
+        <v>48.98583197131639</v>
       </c>
       <c r="M16" t="n">
-        <v>-10.19031666666672</v>
+        <v>-6.311850000000007</v>
       </c>
       <c r="N16" t="n">
-        <v>0.02068605087039543</v>
+        <v>0.05136340314729182</v>
       </c>
       <c r="O16" t="n">
-        <v>1.662007966350068</v>
+        <v>0.2077329953878362</v>
       </c>
       <c r="P16" t="n">
-        <v>15.3</v>
+        <v>-7.033333333333328</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>15.21666666666667</v>
+        <v>14.45</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>23.88333333333333</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.21666666666667</v>
+        <v>-9.43333333333333</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1119981388984077</v>
+        <v>0.1157287174312111</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>0.1004812886674145</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.1119981388984077</v>
+        <v>0.0152474287637966</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.08333333333333333</v>
+        <v>4.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.08333333333333333</v>
+        <v>2.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.1431061962259462</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.8813714304575493</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-0.7382652342316031</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.35</v>
+        <v>0.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.1868101281681779</v>
+        <v>0.04717006116255434</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>0.1671868728596241</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.1868101281681779</v>
+        <v>-0.1200168116970698</v>
       </c>
       <c r="AO16" t="n">
-        <v>41.28333333333333</v>
+        <v>19.35811666666667</v>
       </c>
       <c r="AP16" t="n">
-        <v>31.65</v>
+        <v>11.07741666666667</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.633333333333333</v>
+        <v>8.280700000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>33.31093548904284</v>
+        <v>14.57763861092875</v>
       </c>
       <c r="AS16" t="n">
-        <v>24.16360873509058</v>
+        <v>8.407639114756291</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.14732675395226</v>
+        <v>6.169999496172458</v>
       </c>
       <c r="AU16" t="n">
-        <v>29.13333333333333</v>
+        <v>13.61666666666667</v>
       </c>
       <c r="AV16" t="n">
-        <v>23.28333333333333</v>
+        <v>9.266666666666667</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.849999999999998</v>
+        <v>4.350000000000003</v>
       </c>
       <c r="AX16" t="n">
-        <v>23.76335197186532</v>
+        <v>10.50996594053165</v>
       </c>
       <c r="AY16" t="n">
-        <v>17.08447986676835</v>
+        <v>7.155594247738707</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.678872105096968</v>
+        <v>3.354371692792943</v>
       </c>
       <c r="BA16" t="n">
-        <v>52.25386666666667</v>
+        <v>19.60745</v>
       </c>
       <c r="BB16" t="n">
-        <v>73.19418333333333</v>
+        <v>32.11666666666667</v>
       </c>
       <c r="BC16" t="n">
-        <v>-20.94031666666666</v>
+        <v>-12.50921666666667</v>
       </c>
       <c r="BD16" t="n">
-        <v>49.37794399547691</v>
+        <v>18.75591535897876</v>
       </c>
       <c r="BE16" t="n">
-        <v>65.37319291469859</v>
+        <v>27.38588852763199</v>
       </c>
       <c r="BF16" t="n">
-        <v>-15.99524891922168</v>
+        <v>-8.62997316865323</v>
       </c>
     </row>
     <row r="17">
@@ -3546,7 +3558,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3556,169 +3568,169 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pondicherry to Chennai</t>
+          <t>Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_016_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_016_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>166.3452166666667</v>
+        <v>205.6434166666667</v>
       </c>
       <c r="H17" t="n">
-        <v>188.0674333333333</v>
+        <v>221.15</v>
       </c>
       <c r="I17" t="n">
-        <v>126.5111630773044</v>
+        <v>141.5990549680233</v>
       </c>
       <c r="J17" t="n">
-        <v>126.4609732010443</v>
+        <v>141.6663057069586</v>
       </c>
       <c r="K17" t="n">
-        <v>53.18742578062445</v>
+        <v>51.08928882117495</v>
       </c>
       <c r="L17" t="n">
-        <v>46.12475258422111</v>
+        <v>44.82009341634151</v>
       </c>
       <c r="M17" t="n">
-        <v>-21.72221666666661</v>
+        <v>-15.50658333333331</v>
       </c>
       <c r="N17" t="n">
-        <v>0.05018987626010585</v>
+        <v>-0.0672507389353143</v>
       </c>
       <c r="O17" t="n">
-        <v>7.062673196403338</v>
+        <v>6.26919540483344</v>
       </c>
       <c r="P17" t="n">
-        <v>23.84703333333334</v>
+        <v>10.43813333333333</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>23.84703333333334</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>23.84703333333334</v>
+        <v>-1.616666666666671</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1926372453796382</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.1926372453796382</v>
+        <v>0.1615049145429354</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>12.0548</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>12.0548</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.078327234216284</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.078327234216284</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>-2.3</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>0.2046142102738726</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.2122753364088935</v>
+        <v>0.1164747371577703</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.2122753364088935</v>
+        <v>0.0881394731161023</v>
       </c>
       <c r="AO17" t="n">
-        <v>44.66666666666666</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="AP17" t="n">
-        <v>45.5</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.8333333333333428</v>
+        <v>13.36666666666667</v>
       </c>
       <c r="AR17" t="n">
-        <v>38.02172328104655</v>
+        <v>36.80847059423598</v>
       </c>
       <c r="AS17" t="n">
-        <v>34.12509917533455</v>
+        <v>21.52025885865341</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.896624105712</v>
+        <v>15.28821173558257</v>
       </c>
       <c r="AU17" t="n">
-        <v>28.4</v>
+        <v>30.25</v>
       </c>
       <c r="AV17" t="n">
-        <v>29.80076666666667</v>
+        <v>23</v>
       </c>
       <c r="AW17" t="n">
-        <v>-1.400766666666673</v>
+        <v>7.25</v>
       </c>
       <c r="AX17" t="n">
-        <v>24.68780327217065</v>
+        <v>24.89543913557874</v>
       </c>
       <c r="AY17" t="n">
-        <v>22.74674445845141</v>
+        <v>17.06985215621225</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.941058813719241</v>
+        <v>7.825586979366491</v>
       </c>
       <c r="BA17" t="n">
-        <v>69.43151666666667</v>
+        <v>87.22195000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>86.75</v>
+        <v>134.3833333333333</v>
       </c>
       <c r="BC17" t="n">
-        <v>-17.31848333333333</v>
+        <v>-47.16138333333329</v>
       </c>
       <c r="BD17" t="n">
-        <v>63.6089992787075</v>
+        <v>77.22913797862124</v>
       </c>
       <c r="BE17" t="n">
-        <v>69.25985518858938</v>
+        <v>102.738159054381</v>
       </c>
       <c r="BF17" t="n">
-        <v>-5.650855909881884</v>
+        <v>-25.50902107575976</v>
       </c>
     </row>
     <row r="18">
@@ -3732,7 +3744,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3747,164 +3759,164 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_017_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_017_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>195.4022</v>
+        <v>219.9365833333333</v>
       </c>
       <c r="H18" t="n">
-        <v>266.8632166666667</v>
+        <v>269.2166666666666</v>
       </c>
       <c r="I18" t="n">
-        <v>145.9064422742808</v>
+        <v>146.1177802267258</v>
       </c>
       <c r="J18" t="n">
-        <v>145.9943306994593</v>
+        <v>146.2265476173816</v>
       </c>
       <c r="K18" t="n">
-        <v>46.86485275946674</v>
+        <v>48.97751792605069</v>
       </c>
       <c r="L18" t="n">
-        <v>44.5741238531821</v>
+        <v>44.8576416936978</v>
       </c>
       <c r="M18" t="n">
-        <v>-71.46101666666669</v>
+        <v>-49.28008333333329</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.08788842517850526</v>
+        <v>-0.1087673906557995</v>
       </c>
       <c r="O18" t="n">
-        <v>2.290728906284642</v>
+        <v>4.119876232352887</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.333333333333336</v>
+        <v>-31.04675</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2256049681381114</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2256049681381114</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>8.933333333333334</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="X18" t="n">
-        <v>11.26666666666667</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="Y18" t="n">
-        <v>-2.333333333333336</v>
+        <v>-40.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.2591759316479205</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.323446270295476</v>
+        <v>0.5719741256040581</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.06427033864755549</v>
+        <v>-0.1889083105069204</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>13.90325</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>9.853249999999999</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.189772290028397</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.637209221337241</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9.246550000000001</v>
+        <v>11.6</v>
       </c>
       <c r="AK18" t="n">
-        <v>-9.246550000000001</v>
+        <v>-7.366666666666666</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>0.2739207603422623</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.8240664355600736</v>
+        <v>1.033360466311896</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.8240664355600736</v>
+        <v>-0.7594397059696337</v>
       </c>
       <c r="AO18" t="n">
-        <v>47.05</v>
+        <v>46.35</v>
       </c>
       <c r="AP18" t="n">
         <v>38.68333333333333</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.366666666666667</v>
+        <v>7.666666666666671</v>
       </c>
       <c r="AR18" t="n">
-        <v>37.71427916549126</v>
+        <v>38.07535235688084</v>
       </c>
       <c r="AS18" t="n">
         <v>27.60990969505806</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.1043694704332</v>
+        <v>10.46544266182278</v>
       </c>
       <c r="AU18" t="n">
-        <v>35.66666666666666</v>
+        <v>31.98333333333333</v>
       </c>
       <c r="AV18" t="n">
-        <v>27.13333333333333</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.533333333333328</v>
+        <v>5.166666666666661</v>
       </c>
       <c r="AX18" t="n">
-        <v>27.74280476419689</v>
+        <v>25.72295810760579</v>
       </c>
       <c r="AY18" t="n">
-        <v>19.99447365781878</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7.74833110637811</v>
+        <v>5.830029835698312</v>
       </c>
       <c r="BA18" t="n">
-        <v>103.7522</v>
+        <v>93.28333333333333</v>
       </c>
       <c r="BB18" t="n">
-        <v>120.7166666666667</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="BC18" t="n">
-        <v>-16.9644666666667</v>
+        <v>-23.69999999999997</v>
       </c>
       <c r="BD18" t="n">
-        <v>80.19018241294468</v>
+        <v>79.47271089677133</v>
       </c>
       <c r="BE18" t="n">
-        <v>97.0168296725888</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="BF18" t="n">
-        <v>-16.82664725964412</v>
+        <v>-17.0931010930376</v>
       </c>
     </row>
     <row r="19">
@@ -3918,179 +3930,3899 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_018_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>186.11555</v>
+      </c>
+      <c r="H19" t="n">
+        <v>221.15</v>
+      </c>
+      <c r="I19" t="n">
+        <v>141.7178099447946</v>
+      </c>
+      <c r="J19" t="n">
+        <v>141.7137294264382</v>
+      </c>
+      <c r="K19" t="n">
+        <v>48.97984764694002</v>
+      </c>
+      <c r="L19" t="n">
+        <v>44.83512073701105</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-35.03444999999999</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.004080518356403218</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.14472690992897</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-18.08873333333333</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>8.933333333333334</v>
+      </c>
+      <c r="X19" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-22.86666666666667</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.2591759316479205</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.2215609005542024</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.03761503109371811</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.777933333333333</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>4.777933333333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.7197084907042335</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.7197084907042335</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.1164747371577703</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.1164747371577703</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>45.07095</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>14.60428333333333</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>36.70010973267537</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>21.5632715446163</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>15.13683818805907</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>34.96666666666667</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>11.96666666666667</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>27.29337511764809</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>17.07426318972899</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>10.2191119279191</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>92.36666666666666</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>134.3833333333333</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-42.01666666666664</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>76.745440672119</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>102.738159054381</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-25.992718382262</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>221.1224333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>221.15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>141.8317368861638</v>
+      </c>
+      <c r="J20" t="n">
+        <v>141.6733980516045</v>
+      </c>
+      <c r="K20" t="n">
+        <v>49.27030586470386</v>
+      </c>
+      <c r="L20" t="n">
+        <v>44.82234079251659</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.02756666666670071</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1583388345593164</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.447965072187266</v>
+      </c>
+      <c r="P20" t="n">
+        <v>17.65075</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="X20" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.4844248901091631</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.2215609005542024</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.2628639895549607</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>18.98408333333333</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>18.98408333333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.3753728936893338</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.3753728936893338</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.185676926950206</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.1164747371577703</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.06920218979243568</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>58.60501666666666</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>28.13834999999999</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>43.70509198694462</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>21.5665214603954</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>22.13857052654922</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>31.31100557837641</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>17.03068189911616</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14.28032367926025</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>69.61666666666666</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>134.3833333333333</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-64.76666666666664</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>65.77016461009407</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>102.738159054381</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-36.96799444428693</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PAIR_020</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>STRICT</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>INTERCITY</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Pondicherry to Chennai</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_018_STRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_020_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>184.8726166666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>189.8237333333333</v>
+      </c>
+      <c r="I21" t="n">
+        <v>126.797111280885</v>
+      </c>
+      <c r="J21" t="n">
+        <v>126.7676219192398</v>
+      </c>
+      <c r="K21" t="n">
+        <v>48.60919773277766</v>
+      </c>
+      <c r="L21" t="n">
+        <v>46.13403705248899</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-4.951116666666621</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.02948936164520433</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.475160680288667</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.686899999999994</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>21.48333333333333</v>
+      </c>
+      <c r="X21" t="n">
+        <v>23.71666666666667</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-2.233333333333338</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.237667416199215</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.1169990422600451</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.1206683739391699</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.303566666666667</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.383333333333333</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>5.920233333333334</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.9162394150268994</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.7633432107826125</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.152896204244287</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.683333333333333</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.633333333333333</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.3011879778687425</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.122404176435325</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.1787838014334175</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>48.91905</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>45.25706666666667</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.661983333333332</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>38.90083595250158</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>33.99612977910262</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.904706173398964</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>35.13333333333333</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.233333333333334</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>27.71428406489335</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>22.79241179514765</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.921872269745698</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>86.93333333333334</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-17.58333333333334</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>58.72689645439518</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>68.97633391551152</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-10.24943746111634</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PAIR_021</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_021_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>139.3205333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>149.51085</v>
+      </c>
+      <c r="I22" t="n">
+        <v>106.7510397234517</v>
+      </c>
+      <c r="J22" t="n">
+        <v>106.7303536725813</v>
+      </c>
+      <c r="K22" t="n">
+        <v>51.58938782842431</v>
+      </c>
+      <c r="L22" t="n">
+        <v>49.91426587048593</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-10.19031666666672</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.02068605087039543</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.67512195793838</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-6.571449999999992</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>15.21666666666667</v>
+      </c>
+      <c r="X22" t="n">
+        <v>21.38333333333333</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-6.166666666666659</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.1119981388984077</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.1090721560237224</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.002925982874685304</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-0.4047833333333334</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.3001436458890005</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.724686338784539</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-0.4245426928955385</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.1868101281681779</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.1868101281681779</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>41.28333333333333</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>31.31666666666667</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>9.966666666666661</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>33.31093548904284</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>23.85603505749816</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9.454900431544679</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>28.96666666666667</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>6.016666666666669</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>23.64150595454553</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>16.88692331213</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>6.754582642415528</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>52.07531666666667</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>73.02751666666667</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-20.9522</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>49.1996463669077</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>65.15363680814482</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>-15.95399044123712</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PAIR_022</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_022_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>166.3452166666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>188.0674333333333</v>
+      </c>
+      <c r="I23" t="n">
+        <v>126.5111630773044</v>
+      </c>
+      <c r="J23" t="n">
+        <v>126.4609732010443</v>
+      </c>
+      <c r="K23" t="n">
+        <v>54.3571101011709</v>
+      </c>
+      <c r="L23" t="n">
+        <v>46.52817854574852</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-21.72221666666661</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.05018987626010585</v>
+      </c>
+      <c r="O23" t="n">
+        <v>7.828931555422386</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.430366666666671</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>23.84703333333334</v>
+      </c>
+      <c r="X23" t="n">
+        <v>23.71666666666667</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.1303666666666707</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.1926372453796382</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.1169990422600451</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.0756382031195931</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.683333333333333</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.383333333333333</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.5589577464659954</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.7431465466183387</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-0.1841888001523433</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.1079082363261396</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>-0.1079082363261396</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>44.66666666666666</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>45.08333333333334</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>-0.4166666666666856</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>38.02172328104655</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>33.88390179261686</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.137821488429687</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>27.98333333333333</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>29.80076666666667</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>-1.817433333333341</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>24.42883704029827</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>22.74674445845141</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.68209258184686</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>66.16485</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>85.78333333333333</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>-19.61848333333333</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>63.30900776411389</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>68.86227312477148</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>-5.553265360657583</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_023_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>72.03223333333334</v>
+      </c>
+      <c r="H24" t="n">
+        <v>81.07328333333334</v>
+      </c>
+      <c r="I24" t="n">
+        <v>44.14425672881129</v>
+      </c>
+      <c r="J24" t="n">
+        <v>44.07790624114242</v>
+      </c>
+      <c r="K24" t="n">
+        <v>49.18766031137466</v>
+      </c>
+      <c r="L24" t="n">
+        <v>46.38866788428458</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-9.041049999999998</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.06635048766887053</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.798992427090077</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-6.016666666666669</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="X24" t="n">
+        <v>23.71666666666667</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-9.266666666666669</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.1157287174312111</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.1169990422600451</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-0.001270324828833991</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.1431061962259462</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.2344720787358082</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-0.091365882509862</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.04717006116255434</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.04717006116255434</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>19.35811666666667</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>16.17328333333333</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.184833333333341</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>14.5716785028715</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>11.42860053715295</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.143077965718549</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>13.61666666666667</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10.23333333333333</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3.38333333333334</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>10.50996594053165</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>7.866765487152254</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.643200453379396</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>19.60745</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>-10.54255</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>18.75660731058842</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>24.43106909584137</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>-5.674461785252948</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_024_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>195.4022</v>
+      </c>
+      <c r="H25" t="n">
+        <v>266.8632166666667</v>
+      </c>
+      <c r="I25" t="n">
+        <v>145.9064422742808</v>
+      </c>
+      <c r="J25" t="n">
+        <v>145.9943306994593</v>
+      </c>
+      <c r="K25" t="n">
+        <v>48.03268705989514</v>
+      </c>
+      <c r="L25" t="n">
+        <v>45.34276468747346</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-71.46101666666669</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.08788842517850526</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.689922372421677</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-60.78113333333333</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>8.933333333333334</v>
+      </c>
+      <c r="X25" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-62.14999999999999</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.2591759316479205</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.5490512384335874</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-0.2898753067856669</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.418866666666667</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.368866666666667</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.7086331393992357</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.5525630686911562</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.1560700707080794</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>9.246550000000001</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-9.246550000000001</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.8240664355600736</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-0.8240664355600736</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>46.88333333333333</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>38.68333333333333</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>8.200000000000003</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>37.60330466808259</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>27.60990969505806</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.993394973024532</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>35.66666666666666</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>26.81666666666667</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>8.849999999999987</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>27.74280476419689</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>19.89292827190748</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>7.849876492289411</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>116.9833333333333</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>-18.48333333333331</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>79.5925237709541</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>96.56581198980894</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>-16.97328821885483</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_025_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>255.7438833333333</v>
+      </c>
+      <c r="H26" t="n">
+        <v>265.6299833333333</v>
+      </c>
+      <c r="I26" t="n">
+        <v>145.9773325040056</v>
+      </c>
+      <c r="J26" t="n">
+        <v>145.8893363990339</v>
+      </c>
+      <c r="K26" t="n">
+        <v>47.2452299004206</v>
+      </c>
+      <c r="L26" t="n">
+        <v>45.59497163487288</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-9.886100000000027</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.08799610497169397</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.65025826554772</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-3.295983333333339</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>45.16666666666666</v>
+      </c>
+      <c r="X26" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-25.91666666666667</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.6992727007011277</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.5752841088710083</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.1239885918301193</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>26.67068333333333</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>22.62068333333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.4662856779261432</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.5525630686911562</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-0.08627739076501301</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.883333333333333</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>7.683333333333334</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.2514853038814903</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.6833899734934139</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-0.4319046696119236</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>61.42319999999999</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>38.68333333333333</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>22.73986666666666</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>44.94924920648065</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>27.60990969505806</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>17.33933951142259</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>44.01666666666667</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>26.81666666666667</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>32.63164533881391</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>19.89292827190748</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>12.73871706690643</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>75.58333333333333</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>117.3133166666667</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>-41.72998333333337</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>66.97939427620221</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>96.5752612810128</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>-29.59586700481059</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_026_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
         <v>187.65295</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H27" t="n">
         <v>194.9584</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I27" t="n">
         <v>123.9926446469637</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J27" t="n">
         <v>123.9802750677086</v>
       </c>
-      <c r="K19" t="n">
-        <v>46.87226586428536</v>
-      </c>
-      <c r="L19" t="n">
-        <v>42.81877758960633</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="K27" t="n">
+        <v>46.88285886366883</v>
+      </c>
+      <c r="L27" t="n">
+        <v>42.76169445348732</v>
+      </c>
+      <c r="M27" t="n">
         <v>-7.305450000000008</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N27" t="n">
         <v>0.0123695792550933</v>
       </c>
-      <c r="O19" t="n">
-        <v>4.053488274679033</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="O27" t="n">
+        <v>4.121164410181507</v>
+      </c>
+      <c r="P27" t="n">
+        <v>7.210583333333336</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
         <v>29.48333333333333</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="X27" t="n">
         <v>21.38333333333333</v>
       </c>
-      <c r="S19" t="n">
-        <v>-21.38333333333333</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="Y27" t="n">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.4298392460953699</v>
+      </c>
+      <c r="AA27" t="n">
         <v>0.1090721560237224</v>
       </c>
-      <c r="V19" t="n">
-        <v>-0.1090721560237224</v>
-      </c>
-      <c r="W19" t="n">
-        <v>29.48333333333333</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>29.48333333333333</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.4298392460953699</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0.4298392460953699</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
+      <c r="AB27" t="n">
+        <v>0.3207670900716475</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.1105833333333333</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-0.8894166666666667</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.05848286929177889</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.8778317268481433</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.8193488575563643</v>
+      </c>
+      <c r="AI27" t="n">
         <v>5.266666666666667</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
         <v>5.266666666666667</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AL27" t="n">
         <v>0.3548232692194973</v>
       </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
         <v>0.3548232692194973</v>
       </c>
-      <c r="AO19" t="n">
-        <v>45.59391666666667</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>39.51666666666667</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>6.077249999999999</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>37.16754455699814</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>28.52077529734963</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>8.646769259648508</v>
-      </c>
-      <c r="AU19" t="n">
+      <c r="AO27" t="n">
+        <v>45.48333333333333</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>39.18333333333333</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.299999999999997</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>37.10906168770636</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>28.21320161975721</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.895860067949148</v>
+      </c>
+      <c r="AU27" t="n">
         <v>28.73333333333333</v>
       </c>
-      <c r="AV19" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>-2.06666666666667</v>
-      </c>
-      <c r="AX19" t="n">
+      <c r="AV27" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>-1.733333333333338</v>
+      </c>
+      <c r="AX27" t="n">
         <v>23.38414305111067</v>
       </c>
-      <c r="AY19" t="n">
-        <v>21.13389550628888</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.250247544821789</v>
-      </c>
-      <c r="BA19" t="n">
+      <c r="AY27" t="n">
+        <v>20.93633895165053</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>2.447804099460139</v>
+      </c>
+      <c r="BA27" t="n">
         <v>78.57570000000001</v>
       </c>
-      <c r="BB19" t="n">
-        <v>103.2584</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>-24.68269999999998</v>
-      </c>
-      <c r="BD19" t="n">
+      <c r="BB27" t="n">
+        <v>102.9250666666667</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>-24.34936666666668</v>
+      </c>
+      <c r="BD27" t="n">
         <v>62.65629452354004</v>
       </c>
-      <c r="BE19" t="n">
-        <v>74.21653210804637</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>-11.56023758450632</v>
+      <c r="BE27" t="n">
+        <v>73.84383061342899</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>-11.18753608988895</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PAIR_027</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_29-07-2026\PAIR_027_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>39.97585</v>
+      </c>
+      <c r="H28" t="n">
+        <v>23.74308333333333</v>
+      </c>
+      <c r="I28" t="n">
+        <v>14.82892455320712</v>
+      </c>
+      <c r="J28" t="n">
+        <v>15.14287648205564</v>
+      </c>
+      <c r="K28" t="n">
+        <v>57.87321624947242</v>
+      </c>
+      <c r="L28" t="n">
+        <v>38.26683233039817</v>
+      </c>
+      <c r="M28" t="n">
+        <v>16.23276666666667</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.3139519288485193</v>
+      </c>
+      <c r="O28" t="n">
+        <v>19.60638391907425</v>
+      </c>
+      <c r="P28" t="n">
+        <v>25.86666666666667</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>25.86666666666667</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>25.86666666666667</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.219860917316257</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.219860917316257</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>2.616666666666667</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>4.02745</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>-1.410783333333333</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.15122666286036</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>3.237008300255083</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>-1.085781637394723</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2.816666666666667</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>4.183333333333334</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>-1.366666666666667</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>2.457618245090195</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>2.895199368072901</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>-0.437581122982706</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>8.675850000000001</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>15.5323</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>-6.856449999999999</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>9.000218727940311</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>9.010668813727651</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>-0.01045008578734041</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_05-09-2026\PAIR_028_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>20.26271666666667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>19.8356</v>
+      </c>
+      <c r="I29" t="n">
+        <v>22.49736924506911</v>
+      </c>
+      <c r="J29" t="n">
+        <v>22.45363674285612</v>
+      </c>
+      <c r="K29" t="n">
+        <v>71.17338391598146</v>
+      </c>
+      <c r="L29" t="n">
+        <v>67.91920610273282</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.4271166666666701</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.04373250221298974</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.254177813248646</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.383333333333333</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.383333333333333</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.1022092770638549</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.1022092770638549</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>-0.08333333333333333</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.005475177103936694</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-0.005475177103936694</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>3.639233333333334</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>4.933333333333334</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>-1.294099999999999</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>3.966520593106893</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.72826041501822</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>-0.7617398219113274</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.966666666666667</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.5333333333333332</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>3.418758869278361</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>3.094319836595824</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.3244390326825366</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>11.74015</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>11.85226666666667</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>-0.1121166666666706</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>15.00988050562</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>14.62558131413813</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0.3842991914818707</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_029_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>42.85905</v>
+      </c>
+      <c r="H30" t="n">
+        <v>45.4903</v>
+      </c>
+      <c r="I30" t="n">
+        <v>34.43958194459641</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.32677600023323</v>
+      </c>
+      <c r="K30" t="n">
+        <v>49.88240215190034</v>
+      </c>
+      <c r="L30" t="n">
+        <v>45.25609711599014</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-2.631249999999994</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.1128059443631813</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.6263050359102</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.05476919925384444</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.1405968038522134</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>-0.08582760459836897</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.01267380267082223</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.01267380267082223</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>15.90041666666667</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>4.950416666666671</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>13.25093473030296</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>8.219513195924231</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.03142153437873</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>12.59196666666667</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>3.74196666666667</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.785494672181397</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>6.487184809227589</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>3.298309862953808</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>25.52363333333333</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>-12.82363333333333</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>11.33570954018739</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>19.4794811912292</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>-8.143771651041812</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\29-07-2026_to_06-09-2026\PAIR_030_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>231.7772166666667</v>
+      </c>
+      <c r="H31" t="n">
+        <v>213.89885</v>
+      </c>
+      <c r="I31" t="n">
+        <v>231.4242273523428</v>
+      </c>
+      <c r="J31" t="n">
+        <v>231.3323956071126</v>
+      </c>
+      <c r="K31" t="n">
+        <v>67.59910743007244</v>
+      </c>
+      <c r="L31" t="n">
+        <v>70.84744357406082</v>
+      </c>
+      <c r="M31" t="n">
+        <v>17.87836666666669</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.09183174523019488</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-3.248336143988382</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-12.46666666666667</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>21.51666666666667</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>21.51666666666667</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.814768997799896</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.814768997799896</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="X31" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-14.43333333333333</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.1409484311311202</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.2136487015115684</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-0.07270027038044818</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.966666666666667</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.71055</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>3.293883333333333</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.5708869176953876</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.2061655756673897</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.3647213420279979</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>-9.799999999999997</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>25.92939460092482</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>38.59680733466195</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>-12.66741273373713</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>25.63333333333333</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>-0.7833333333333279</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>25.11723460299349</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>26.87122394746974</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>-1.753989344476249</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>148.25</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>132.1321833333333</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>16.1178166666667</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>178.8509938017981</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>165.4445500478019</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>13.4064437539962</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to SilkBoard</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\31-07-2026_to_04-09-2026\PAIR_031_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>14.8788</v>
+      </c>
+      <c r="H32" t="n">
+        <v>16.75645</v>
+      </c>
+      <c r="I32" t="n">
+        <v>12.73848083938423</v>
+      </c>
+      <c r="J32" t="n">
+        <v>12.6496249595659</v>
+      </c>
+      <c r="K32" t="n">
+        <v>51.36898475435208</v>
+      </c>
+      <c r="L32" t="n">
+        <v>45.29464758788131</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1.877650000000001</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.08885587981833076</v>
+      </c>
+      <c r="O32" t="n">
+        <v>6.074337166470769</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>-0.08333333333333333</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.01248000402488661</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>-0.01248000402488661</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.57280616355066</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.59336123238131</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>-1.02055506883065</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.43445</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.623083333333333</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>-0.1886333333333332</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.851109043655713</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.975517359737947</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>-0.124408316082234</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>10.34435</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>10.78336666666667</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>-0.4390166666666691</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>9.314565632177855</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>8.068266363421753</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.246299268756102</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PAIR_032</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-09-2026_to_06-09-2026\PAIR_032_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>251.8893</v>
+      </c>
+      <c r="H33" t="n">
+        <v>234.6249833333333</v>
+      </c>
+      <c r="I33" t="n">
+        <v>240.4425765887812</v>
+      </c>
+      <c r="J33" t="n">
+        <v>240.7230050078111</v>
+      </c>
+      <c r="K33" t="n">
+        <v>64.24069875201077</v>
+      </c>
+      <c r="L33" t="n">
+        <v>68.13871680530009</v>
+      </c>
+      <c r="M33" t="n">
+        <v>17.2643166666667</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-0.2804284190299029</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-3.89801805328932</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-16.05</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>21.51666666666667</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>21.51666666666667</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.814768997799896</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.814768997799896</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="X33" t="n">
+        <v>16.43333333333333</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-12.76666666666666</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.1409484311311202</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.08388219724002884</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.05706623389109138</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.033333333333333</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>6.316666666666666</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>-3.283333333333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.005421542589709919</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.02429801927644335</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>-0.01887647668673343</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>7.283333333333333</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.283333333333333</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.9244772773315977</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.2309310830082773</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.6935461943233203</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>30.68333333333333</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>43.75068333333333</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>-13.06735</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>28.50220385729329</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>43.296144650172</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>-14.79394079287871</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>27.88333333333333</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>31.78333333333333</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>-3.900000000000002</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>26.94936248085756</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>33.18950889523448</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>-6.240146414376923</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>157.8226333333333</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>131.3409666666667</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>26.4816666666666</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>183.105394001778</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>163.8982401628798</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>19.20715383889819</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PAIR_033</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026\PAIR_033_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>184.8808833333333</v>
+      </c>
+      <c r="H34" t="n">
+        <v>189.0966166666667</v>
+      </c>
+      <c r="I34" t="n">
+        <v>159.8172074707595</v>
+      </c>
+      <c r="J34" t="n">
+        <v>159.58380997156</v>
+      </c>
+      <c r="K34" t="n">
+        <v>58.20216621959079</v>
+      </c>
+      <c r="L34" t="n">
+        <v>55.92805804691302</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-4.215733333333418</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.2333974991995262</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.274108172677764</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.166666666666671</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X34" t="n">
+        <v>14.68333333333333</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-10.73333333333333</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.06497427594259966</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.1830132758657204</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-0.1180389999231207</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.1028343892545171</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.04005612640255141</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.06277826285196569</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>10.68333333333333</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>-7.43333333333333</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.2821742444234817</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.6170753744976548</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>-0.3349011300741731</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>26.06666666666667</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>14.13333333333333</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>34.54349490383015</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>22.28483087263108</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>12.25866403119907</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>29.63088333333333</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>7.047550000000001</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>26.48638220201241</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>19.99284056290314</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>6.493541639109271</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>111.62995</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>-20.12994999999999</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>98.33734745529641</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>116.4659937592599</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>-18.12864630396349</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_18-09-2026\PAIR_034_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>66.01939999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>94.14933333333333</v>
+      </c>
+      <c r="I35" t="n">
+        <v>49.09342708546251</v>
+      </c>
+      <c r="J35" t="n">
+        <v>49.01363547616007</v>
+      </c>
+      <c r="K35" t="n">
+        <v>47.58550177729312</v>
+      </c>
+      <c r="L35" t="n">
+        <v>37.18511343393678</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-28.12993333333334</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.07979160930243978</v>
+      </c>
+      <c r="O35" t="n">
+        <v>10.40038834335634</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X35" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>-10.75</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.06497427594259966</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.3781894421708778</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-0.3132151662282782</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.01632338704389566</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>-0.01632338704389566</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-0.6499999999999999</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.07825898700519315</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.1903594564923157</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>-0.1121004694871225</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>21.19846666666666</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>24.53266666666667</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>-3.33420000000001</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>17.20758212650452</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>16.02491169354092</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.182670432963601</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>15.75426666666667</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>17.41666666666667</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>-1.662400000000002</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>12.63780002856964</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>11.032089516834</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.605710511735639</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>23.86666666666667</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>-10.98333333333333</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>19.10481166744055</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>21.37176198007807</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>-2.266950312637519</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026\PAIR_035_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>13.15565</v>
+      </c>
+      <c r="H36" t="n">
+        <v>14.03436666666667</v>
+      </c>
+      <c r="I36" t="n">
+        <v>17.5104260598227</v>
+      </c>
+      <c r="J36" t="n">
+        <v>17.59592292311513</v>
+      </c>
+      <c r="K36" t="n">
+        <v>79.86116714790693</v>
+      </c>
+      <c r="L36" t="n">
+        <v>75.22643525442838</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-0.878716666666671</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-0.08549686329243045</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4.634731893478545</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>2.366666666666667</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.783333333333334</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>3.068290636520454</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.6703253541496691</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.397965282370785</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.683333333333333</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>2.206663901320678</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.4473149966220811</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.759348904698597</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>9.105650000000001</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>13.10103333333333</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>-3.995383333333329</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>12.23547152198156</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>16.47828257234338</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>-4.242811050361821</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PAIR_036</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_036_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>11.71183333333333</v>
+      </c>
+      <c r="H37" t="n">
+        <v>11.73173333333333</v>
+      </c>
+      <c r="I37" t="n">
+        <v>16.43424965629278</v>
+      </c>
+      <c r="J37" t="n">
+        <v>16.43868693033036</v>
+      </c>
+      <c r="K37" t="n">
+        <v>84.19305084978724</v>
+      </c>
+      <c r="L37" t="n">
+        <v>84.07293174806406</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-0.01989999999999981</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-0.004437274037577765</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.1201191017231764</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.683333333333333</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>-0.1833333333333329</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.145589159808596</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.354103498469736</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>-0.2085143386611401</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.233333333333333</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.23205</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>-0.9987166666666671</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.726998909362367</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>2.895877582706585</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>-1.168878673344218</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>8.9785</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>7.81635</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.16215</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>12.56166158712181</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>11.18870584915403</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.37295573796778</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PAIR_037</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_037_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>116.7043666666667</v>
+      </c>
+      <c r="H38" t="n">
+        <v>117.7956</v>
+      </c>
+      <c r="I38" t="n">
+        <v>106.4407237351212</v>
+      </c>
+      <c r="J38" t="n">
+        <v>106.429493371315</v>
+      </c>
+      <c r="K38" t="n">
+        <v>57.74313792935574</v>
+      </c>
+      <c r="L38" t="n">
+        <v>61.22560386453947</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-1.091233333333292</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.01123036380619169</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-3.482465935183733</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-7.516666666666663</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>13.68333333333333</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-13.68333333333333</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.1905534317712249</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-0.1905534317712249</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.06082944355873176</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.06082944355873176</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.07885964335257711</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.005855051964785372</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.07300459138779174</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>32.13333333333333</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>15.36666666666667</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>16.76666666666666</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>27.22400876286396</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>12.99028801976566</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>14.2337207430983</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>12.98333333333333</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>12.46666666666667</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>21.71770276874582</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>11.46884073038654</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>10.24886203835928</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>52.2877</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>75.42893333333333</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>-23.14123333333333</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>57.35932311660007</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>81.77395613742682</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>-24.41463302082675</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PAIR_038</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026\PAIR_038_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>154.2935833333334</v>
+      </c>
+      <c r="H39" t="n">
+        <v>89.89455</v>
+      </c>
+      <c r="I39" t="n">
+        <v>118.6528555237152</v>
+      </c>
+      <c r="J39" t="n">
+        <v>118.3205529638225</v>
+      </c>
+      <c r="K39" t="n">
+        <v>76.62526023529979</v>
+      </c>
+      <c r="L39" t="n">
+        <v>78.97289855535573</v>
+      </c>
+      <c r="M39" t="n">
+        <v>64.39903333333341</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.3323025598927103</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-2.347638320055935</v>
+      </c>
+      <c r="P39" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.09002709918491375</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.09002709918491375</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.1211416233489353</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.1211416233489353</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>-0.6833333333333333</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.01887125568339211</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.03644173622497521</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-0.0175704805415831</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>19.22816666666667</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>14.0627</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>5.165466666666671</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>21.56383013715203</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>15.34811928295864</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>6.215710854193391</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>15.13208333333333</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>5.032083333333331</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>17.72416642729523</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>11.19959394493595</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>6.524572482359281</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>58.06666666666667</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>64.73184999999999</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>-6.665183333333324</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>79.13481898105066</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>91.736397999703</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>-12.60157901865234</v>
       </c>
     </row>
   </sheetData>
